--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513600_ELIMINATORIAS12FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513600_ELIMINATORIAS12FINAL_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0569</v>
+        <v>5.7943</v>
       </c>
       <c r="E2" t="n">
-        <v>1.794</v>
+        <v>3.128</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2629</v>
+        <v>2.6663</v>
       </c>
       <c r="G2" t="n">
         <v>4.7549</v>
@@ -610,13 +610,13 @@
         <v>3.0368</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3403</v>
+        <v>0.3971</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1422</v>
+        <v>0.1918</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1981</v>
+        <v>0.2053</v>
       </c>
       <c r="V2" t="n">
         <v>-0.37</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7811</v>
+        <v>3.089</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6774</v>
+        <v>0.1721</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1037</v>
+        <v>2.9169</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9857</v>
+        <v>2.5527</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4613</v>
+        <v>1.5602</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4756</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4269</v>
+        <v>2.2993</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1118</v>
+        <v>2.4674</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6848</v>
+        <v>-0.168</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4412</v>
+        <v>0.2533</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6504</v>
+        <v>-0.9071</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2092</v>
+        <v>1.1605</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4049</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0245</v>
+        <v>-5.0613</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4294</v>
+        <v>3.2392</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9855</v>
+        <v>0.6921</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0847</v>
+        <v>0.6469</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9008</v>
+        <v>0.0452</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5951</v>
+        <v>1.6663</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1902</v>
+        <v>2.2872</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7853</v>
+        <v>-0.6209</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9998</v>
+        <v>2.2421</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.7592</v>
+        <v>1.5994</v>
       </c>
       <c r="F4" t="n">
-        <v>4.759</v>
+        <v>0.6427</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6379</v>
+        <v>0.9857</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1055</v>
+        <v>1.4613</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7434</v>
+        <v>-0.4756</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.157</v>
+        <v>1.4269</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4524</v>
+        <v>2.1118</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.6093</v>
+        <v>-0.6848</v>
       </c>
       <c r="M4" t="n">
-        <v>1.519</v>
+        <v>-0.4412</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6531</v>
+        <v>-0.6504</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8659</v>
+        <v>0.2092</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0123</v>
+        <v>0.4049</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0123</v>
+        <v>-2.0245</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0245</v>
+        <v>2.4294</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4004</v>
+        <v>1.4466</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7542</v>
+        <v>1.0068</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6462</v>
+        <v>0.4398</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2251</v>
+        <v>-0.5951</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3442</v>
+        <v>1.1902</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5693</v>
+        <v>-1.7853</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7846</v>
+        <v>1.7697</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7864</v>
+        <v>0.9919</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5711</v>
+        <v>0.7778</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5527</v>
+        <v>1.4072</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5602</v>
+        <v>0.5929</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.8143</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2993</v>
+        <v>0.9919</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4674</v>
+        <v>0.3161</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.168</v>
+        <v>0.6758</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2533</v>
+        <v>0.4153</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9071</v>
+        <v>0.2768</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1605</v>
+        <v>0.1384</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8221</v>
+        <v>0.2025</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.0613</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2392</v>
+        <v>0.2025</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6123</v>
+        <v>0.1601</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3117</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3005</v>
+        <v>0.1601</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6663</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2872</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6209</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.648</v>
+        <v>1.3033</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9278999999999999</v>
+        <v>-3.254</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7202</v>
+        <v>4.5573</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4072</v>
+        <v>-0.6379</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5929</v>
+        <v>1.1055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8143</v>
+        <v>-1.7434</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9919</v>
+        <v>-2.157</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3161</v>
+        <v>0.4524</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6758</v>
+        <v>-2.6093</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4153</v>
+        <v>1.519</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2768</v>
+        <v>0.6531</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1384</v>
+        <v>0.8659</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2025</v>
+        <v>1.0123</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2025</v>
+        <v>2.0245</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0384</v>
+        <v>0.7039</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.064</v>
+        <v>0.2594</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1025</v>
+        <v>0.4445</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2251</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3442</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.5693</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5097</v>
+        <v>0.8404</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2711</v>
+        <v>-2.2593</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7808</v>
+        <v>3.0997</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8769</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8711</v>
+        <v>0.3549</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0058</v>
+        <v>0.5699</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4368</v>
+        <v>0.6704</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5163</v>
+        <v>0.5511</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0795</v>
+        <v>0.1193</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4401</v>
+        <v>0.2544</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3548</v>
+        <v>-0.1962</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0853</v>
+        <v>0.4507</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2147</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>-3.0368</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8221</v>
+        <v>2.4294</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1639</v>
+        <v>0.642</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2024</v>
+        <v>0.1071</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9614</v>
+        <v>0.5349</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4374</v>
+        <v>-0.119</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4374</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3979</v>
+        <v>-0.1043</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9323</v>
+        <v>-2.4528</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3302</v>
+        <v>2.3486</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9249000000000001</v>
+        <v>-0.8769</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3549</v>
+        <v>-0.8711</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5699</v>
+        <v>-0.0058</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6704</v>
+        <v>-0.4368</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5511</v>
+        <v>-0.5163</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1193</v>
+        <v>0.0795</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2544</v>
+        <v>-0.4401</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1962</v>
+        <v>-0.3548</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4507</v>
+        <v>-0.0853</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q8" t="n">
         <v>-3.0368</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4294</v>
+        <v>1.8221</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1994</v>
+        <v>1.5499</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4341</v>
+        <v>1.0207</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7654</v>
+        <v>0.5292</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.119</v>
+        <v>0.4374</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.119</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9157</v>
+        <v>-0.2059</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3462</v>
+        <v>-1.8669</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4305</v>
+        <v>1.661</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0888</v>
@@ -1156,13 +1156,13 @@
         <v>1.0123</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7202</v>
+        <v>-0.0104</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4482</v>
+        <v>0.0311</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2719</v>
+        <v>-0.0414</v>
       </c>
       <c r="V9" t="n">
         <v>-0.119</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1241</v>
+        <v>-0.8606</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8842</v>
+        <v>0.6107</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2399</v>
+        <v>-1.4713</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9512</v>
+        <v>1.298</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3.8337</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9512</v>
+        <v>-2.5356</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6921</v>
+        <v>2.7082</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4.761</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6921</v>
+        <v>-2.0528</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2591</v>
+        <v>-1.4101</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.9273</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2591</v>
+        <v>-0.4829</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.0368</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.227</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1729</v>
+        <v>0.4364</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1921</v>
+        <v>0.3441</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0192</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.7853</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5951</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4112</v>
+        <v>-1.0953</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4869</v>
+        <v>-0.8842</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0757</v>
+        <v>-0.2111</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9392</v>
+        <v>-0.9512</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1264</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8128</v>
+        <v>-0.9512</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3052</v>
+        <v>-0.6921</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6131</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>-0.6921</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6341</v>
+        <v>-0.2591</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5134</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1207</v>
+        <v>-0.2591</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8098</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8098</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2817</v>
+        <v>-0.1441</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1817</v>
+        <v>-0.1921</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1</v>
+        <v>0.048</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1645</v>
+        <v>-1.2497</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4915</v>
+        <v>-1.3831</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.673</v>
+        <v>0.1334</v>
       </c>
       <c r="G12" t="n">
-        <v>1.298</v>
+        <v>-1.9392</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8337</v>
+        <v>-1.1264</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.5356</v>
+        <v>-0.8128</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7082</v>
+        <v>-1.3052</v>
       </c>
       <c r="K12" t="n">
-        <v>4.761</v>
+        <v>-0.6131</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0528</v>
+        <v>-0.6921</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4101</v>
+        <v>-0.6341</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9273</v>
+        <v>-0.5134</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4829</v>
+        <v>-0.1207</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8098</v>
+        <v>0.8098</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0368</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.227</v>
+        <v>0.8098</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-0.1203</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.758</v>
+        <v>-0.0779</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1094</v>
+        <v>-0.0424</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7853</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5951</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.5625</v>
+        <v>11.523</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.558500000000001</v>
+        <v>-5.5982</v>
       </c>
       <c r="F13" t="n">
-        <v>17.1212</v>
+        <v>17.1213</v>
       </c>
       <c r="G13" t="n">
-        <v>6.429400000000001</v>
+        <v>6.429400000000003</v>
       </c>
       <c r="H13" t="n">
-        <v>5.825600000000001</v>
+        <v>5.8256</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6035999999999997</v>
+        <v>0.6035999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>5.9732</v>
+        <v>5.973199999999999</v>
       </c>
       <c r="K13" t="n">
         <v>8.5808</v>
@@ -1450,13 +1450,13 @@
         <v>-2.607400000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4558999999999997</v>
+        <v>0.4558999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-2.7551</v>
       </c>
       <c r="O13" t="n">
-        <v>3.211</v>
+        <v>3.211000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>9.999999999987796e-05</v>
@@ -1468,13 +1468,13 @@
         <v>19.233</v>
       </c>
       <c r="S13" t="n">
-        <v>4.792800000000001</v>
+        <v>5.753299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3775</v>
+        <v>3.3379</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4156</v>
+        <v>2.4155</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6596</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7244</v>
+        <v>3.7014</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2057</v>
+        <v>2.1019</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5187</v>
+        <v>1.5995</v>
       </c>
       <c r="G14" t="n">
         <v>2.3664</v>
@@ -1546,13 +1546,13 @@
         <v>1.4172</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1433</v>
+        <v>0.1203</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1403</v>
+        <v>-0.2441</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2836</v>
+        <v>0.3644</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7399</v>
+        <v>1.1782</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2905</v>
+        <v>-1.1867</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0304</v>
+        <v>2.3649</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0702</v>
@@ -1624,13 +1624,13 @@
         <v>2.6319</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8458</v>
+        <v>-0.4075</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5885</v>
+        <v>-0.4847</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2572</v>
+        <v>0.0772</v>
       </c>
       <c r="V15" t="n">
         <v>1.4411</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6962</v>
+        <v>1.1518</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8371</v>
+        <v>1.1485</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1408</v>
+        <v>0.0033</v>
       </c>
       <c r="G16" t="n">
         <v>2.3563</v>
@@ -1702,13 +1702,13 @@
         <v>1.2147</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8625</v>
+        <v>-0.407</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6403</v>
+        <v>-0.3289</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2222</v>
+        <v>-0.0781</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5951</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7145</v>
+        <v>-1.093</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3809</v>
+        <v>-1.5494</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6664</v>
+        <v>0.4564</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3782</v>
+        <v>-0.4263</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8762</v>
+        <v>-1.3038</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.502</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1266</v>
+        <v>-0.1685</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5538</v>
+        <v>-0.6131</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5728</v>
+        <v>0.4445</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2516</v>
+        <v>-0.2578</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3224</v>
+        <v>-0.6908</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0708</v>
+        <v>0.433</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6319</v>
+        <v>0.2025</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6319</v>
+        <v>1.2147</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3153</v>
+        <v>-0.6182</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4341</v>
+        <v>-0.3687</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1188</v>
+        <v>-0.2495</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2834</v>
+        <v>-0.2509</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6883</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5951</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5831</v>
+        <v>-1.1122</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7571</v>
+        <v>-1.6046</v>
       </c>
       <c r="F18" t="n">
-        <v>0.174</v>
+        <v>0.4923</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4263</v>
+        <v>-0.778</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3038</v>
+        <v>0.0583</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8774999999999999</v>
+        <v>-0.8363</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1685</v>
+        <v>0.0169</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6131</v>
+        <v>1.3216</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4445</v>
+        <v>-1.3047</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2578</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6908</v>
+        <v>-1.2633</v>
       </c>
       <c r="O18" t="n">
-        <v>0.433</v>
+        <v>0.4684</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2025</v>
+        <v>1.2147</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0123</v>
+        <v>-1.2147</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2147</v>
+        <v>2.4294</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1083</v>
+        <v>-0.9539</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5763</v>
+        <v>-0.4068</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.532</v>
+        <v>-0.5471</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2509</v>
+        <v>-0.5951</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2509</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9484</v>
+        <v>-1.1873</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0198</v>
+        <v>-1.9</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.7127</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.778</v>
+        <v>-2.3782</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0583</v>
+        <v>-1.8762</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8363</v>
+        <v>-0.502</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0169</v>
+        <v>-1.1266</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3216</v>
+        <v>-0.5538</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3047</v>
+        <v>-0.5728</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-1.2516</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2633</v>
+        <v>-1.3224</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4684</v>
+        <v>0.0708</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2147</v>
+        <v>2.6319</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2147</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4294</v>
+        <v>2.6319</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.79</v>
+        <v>-0.1575</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.968</v>
+        <v>-0.0725</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5951</v>
+        <v>-1.2834</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6883</v>
       </c>
       <c r="X19" t="n">
         <v>-0.5951</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>A. MOODY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1101</v>
+        <v>-1.4414</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6635</v>
+        <v>-1.9141</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5534</v>
+        <v>0.4727</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.705</v>
+        <v>-2.093</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9876</v>
+        <v>-1.4023</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2826</v>
+        <v>-0.6906</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5052</v>
+        <v>-0.8011</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3372</v>
+        <v>-0.5933</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.168</v>
+        <v>-0.2078</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1998</v>
+        <v>-1.2919</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6504</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4507</v>
+        <v>-0.4829</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8221</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4417</v>
+        <v>-2.0245</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6196</v>
+        <v>1.8221</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8665</v>
+        <v>-0.3362</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5019</v>
+        <v>-0.2787</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3646</v>
+        <v>-0.0574</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2834</v>
+        <v>1.1902</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7853</v>
+        <v>1.1902</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2529</v>
+        <v>-1.741</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5703</v>
+        <v>-2.352</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3174</v>
+        <v>0.611</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0987</v>
+        <v>-0.705</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0191</v>
+        <v>-0.9876</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1178</v>
+        <v>0.2826</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0161</v>
+        <v>-0.5052</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7085</v>
+        <v>-0.3372</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7246</v>
+        <v>-0.168</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.1998</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6894</v>
+        <v>-0.6504</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6068</v>
+        <v>0.4507</v>
       </c>
       <c r="P21" t="n">
+        <v>-1.8221</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-3.4417</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-6.276</v>
-      </c>
       <c r="R21" t="n">
-        <v>2.8343</v>
+        <v>1.6196</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8181</v>
+        <v>-0.4974</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0621</v>
+        <v>-0.1905</v>
       </c>
       <c r="U21" t="n">
-        <v>0.756</v>
+        <v>-0.3069</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5306</v>
+        <v>1.2834</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6596</v>
+        <v>1.7853</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1902</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MOODY</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2544</v>
+        <v>-2.3764</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3294</v>
+        <v>-2.4009</v>
       </c>
       <c r="F22" t="n">
-        <v>0.075</v>
+        <v>0.0245</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.093</v>
+        <v>-1.6601</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4023</v>
+        <v>-1.3832</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6906</v>
+        <v>-0.2768</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8011</v>
+        <v>-1.3644</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5933</v>
+        <v>-0.6723</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2078</v>
+        <v>-0.6921</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2919</v>
+        <v>-0.2957</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.7109</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4829</v>
+        <v>0.4153</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2025</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0245</v>
+        <v>-1.0123</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8221</v>
+        <v>0.4049</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1492</v>
+        <v>-0.109</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.694</v>
+        <v>-0.0243</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4552</v>
+        <v>-0.0847</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1902</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1902</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.365</v>
+        <v>-2.6966</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5047</v>
+        <v>-1.9591</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1398</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6601</v>
+        <v>-1.9426</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3832</v>
+        <v>-1.4818</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2768</v>
+        <v>-0.4608</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3644</v>
+        <v>-0.6128</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6723</v>
+        <v>-0.6526</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6921</v>
+        <v>0.0398</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2957</v>
+        <v>-1.3297</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7109</v>
+        <v>-0.8292</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4153</v>
+        <v>-0.5006</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0123</v>
+        <v>-1.2147</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4049</v>
+        <v>1.0123</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0975</v>
+        <v>-0.5516</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1281</v>
+        <v>-0.1316</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0305</v>
+        <v>-0.42</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4947</v>
+        <v>-3.5618</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6477</v>
+        <v>-5.5047</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.847</v>
+        <v>1.9429</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9426</v>
+        <v>-0.0987</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4818</v>
+        <v>0.0191</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4608</v>
+        <v>-0.1178</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6128</v>
+        <v>-0.0161</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6526</v>
+        <v>0.7085</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0398</v>
+        <v>-0.7246</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3297</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8292</v>
+        <v>-0.6894</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5006</v>
+        <v>0.6068</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2025</v>
+        <v>-3.4417</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.2147</v>
+        <v>-6.276</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0123</v>
+        <v>2.8343</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3497</v>
+        <v>0.5092</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1798</v>
+        <v>0.1278</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5296</v>
+        <v>0.3814</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.5306</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.6596</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.5626</v>
+        <v>-9.1783</v>
       </c>
       <c r="E25" t="n">
         <v>-17.1211</v>
       </c>
       <c r="F25" t="n">
-        <v>6.5587</v>
+        <v>7.942799999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.429399999999999</v>
+        <v>-6.4294</v>
       </c>
       <c r="H25" t="n">
         <v>-5.825699999999999</v>
@@ -2377,13 +2377,13 @@
         <v>-0.6035999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4558000000000002</v>
+        <v>-0.4558000000000004</v>
       </c>
       <c r="K25" t="n">
-        <v>2.755099999999999</v>
+        <v>2.7551</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.210900000000001</v>
+        <v>-3.2109</v>
       </c>
       <c r="M25" t="n">
         <v>-5.9734</v>
@@ -2395,7 +2395,7 @@
         <v>2.6075</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.0002000000000005331</v>
+        <v>-0.0002000000000008662</v>
       </c>
       <c r="Q25" t="n">
         <v>-19.2331</v>
@@ -2404,16 +2404,16 @@
         <v>19.233</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.7928</v>
+        <v>-3.4088</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.4155</v>
+        <v>-2.415500000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.3775</v>
+        <v>-0.9932000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6596000000000001</v>
+        <v>0.6596000000000004</v>
       </c>
       <c r="W25" t="n">
         <v>4.983000000000001</v>
